--- a/backend/data/financials_by_company/1589.TW.xlsx
+++ b/backend/data/financials_by_company/1589.TW.xlsx
@@ -657,568 +657,568 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-6576000</v>
+        <v>-2662682.412201</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.332627</v>
       </c>
       <c r="D2" t="n">
-        <v>994431000</v>
+        <v>933194000</v>
       </c>
       <c r="E2" t="n">
-        <v>-26304000</v>
+        <v>-8005000</v>
       </c>
       <c r="F2" t="n">
-        <v>-26304000</v>
+        <v>-8005000</v>
       </c>
       <c r="G2" t="n">
-        <v>-626317000</v>
+        <v>216102000</v>
       </c>
       <c r="H2" t="n">
-        <v>697906000</v>
+        <v>536630000</v>
       </c>
       <c r="I2" t="n">
-        <v>7253856000</v>
+        <v>7178390000</v>
       </c>
       <c r="J2" t="n">
-        <v>968127000</v>
+        <v>925189000</v>
       </c>
       <c r="K2" t="n">
-        <v>270221000</v>
+        <v>388559000</v>
       </c>
       <c r="L2" t="n">
-        <v>-385953000</v>
+        <v>-11627000</v>
       </c>
       <c r="M2" t="n">
-        <v>432581000</v>
+        <v>67939000</v>
       </c>
       <c r="N2" t="n">
-        <v>46628000</v>
+        <v>56312000</v>
       </c>
       <c r="O2" t="n">
-        <v>-606589000</v>
+        <v>221444317.587799</v>
       </c>
       <c r="P2" t="n">
-        <v>-626317000</v>
+        <v>216102000</v>
       </c>
       <c r="Q2" t="n">
-        <v>8377012000</v>
+        <v>8625701000</v>
       </c>
       <c r="R2" t="n">
-        <v>121087000</v>
+        <v>127533348</v>
       </c>
       <c r="S2" t="n">
-        <v>121087000</v>
+        <v>111846985</v>
       </c>
       <c r="T2" t="n">
-        <v>-5.17</v>
+        <v>1.859342</v>
       </c>
       <c r="U2" t="n">
-        <v>-5.17</v>
+        <v>1.928573</v>
       </c>
       <c r="V2" t="n">
-        <v>-626317000</v>
+        <v>216102000</v>
       </c>
       <c r="W2" t="n">
-        <v>-626317000</v>
+        <v>216102000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-626317000</v>
+        <v>216102000</v>
       </c>
       <c r="Z2" t="n">
-        <v>6972000</v>
+        <v>2129000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-633289000</v>
+        <v>213973000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-633289000</v>
+        <v>213973000</v>
       </c>
       <c r="AC2" t="n">
-        <v>470929000</v>
+        <v>106647000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-162360000</v>
+        <v>320620000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1526023000</v>
+        <v>14348000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-4685000</v>
+        <v>-6453000</v>
       </c>
       <c r="AG2" t="n">
-        <v>4685000</v>
+        <v>6453000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-385953000</v>
+        <v>-11627000</v>
       </c>
       <c r="AI2" t="n">
-        <v>432581000</v>
+        <v>67939000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>46628000</v>
+        <v>56312000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1174776000</v>
+        <v>322510000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1123156000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>1447311000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>6453000</v>
+      </c>
       <c r="AN2" t="n">
-        <v>227037000</v>
+        <v>351541000</v>
       </c>
       <c r="AO2" t="n">
-        <v>896119000</v>
+        <v>1095770000</v>
       </c>
       <c r="AP2" t="n">
-        <v>371847000</v>
+        <v>476495000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>524272000</v>
+        <v>619275000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-51620000</v>
+        <v>1769821000</v>
       </c>
       <c r="AS2" t="n">
-        <v>7253856000</v>
+        <v>7178390000</v>
       </c>
       <c r="AT2" t="n">
-        <v>7202236000</v>
+        <v>8948211000</v>
       </c>
       <c r="AU2" t="n">
-        <v>7202236000</v>
+        <v>8948211000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-15821250</v>
+        <v>1318750</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>548875000</v>
+        <v>359559000</v>
       </c>
       <c r="E3" t="n">
-        <v>-63285000</v>
+        <v>5275000</v>
       </c>
       <c r="F3" t="n">
-        <v>-63285000</v>
+        <v>5275000</v>
       </c>
       <c r="G3" t="n">
-        <v>-269740000</v>
+        <v>-438462000</v>
       </c>
       <c r="H3" t="n">
-        <v>505127000</v>
+        <v>530361000</v>
       </c>
       <c r="I3" t="n">
-        <v>7473371000</v>
+        <v>8040146000</v>
       </c>
       <c r="J3" t="n">
-        <v>485590000</v>
+        <v>364834000</v>
       </c>
       <c r="K3" t="n">
-        <v>-19537000</v>
+        <v>-165527000</v>
       </c>
       <c r="L3" t="n">
-        <v>-209975000</v>
+        <v>-114745000</v>
       </c>
       <c r="M3" t="n">
-        <v>243667000</v>
+        <v>148654000</v>
       </c>
       <c r="N3" t="n">
-        <v>33692000</v>
+        <v>33909000</v>
       </c>
       <c r="O3" t="n">
-        <v>-222276250</v>
+        <v>-442418250</v>
       </c>
       <c r="P3" t="n">
-        <v>-269740000</v>
+        <v>-438462000</v>
       </c>
       <c r="Q3" t="n">
-        <v>8779235000</v>
+        <v>9287381000</v>
       </c>
       <c r="R3" t="n">
-        <v>117284677</v>
+        <v>111846985</v>
       </c>
       <c r="S3" t="n">
-        <v>117284677</v>
+        <v>111846985</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.295527</v>
+        <v>-3.916487</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.295527</v>
+        <v>-3.916487</v>
       </c>
       <c r="V3" t="n">
-        <v>-269740000</v>
+        <v>-438462000</v>
       </c>
       <c r="W3" t="n">
-        <v>-269740000</v>
+        <v>-438462000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-269740000</v>
+        <v>-438462000</v>
       </c>
       <c r="Z3" t="n">
-        <v>6601000</v>
+        <v>5913000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-276341000</v>
+        <v>-444375000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-276341000</v>
+        <v>-444375000</v>
       </c>
       <c r="AC3" t="n">
-        <v>13137000</v>
+        <v>130194000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-263204000</v>
+        <v>-314181000</v>
       </c>
       <c r="AE3" t="n">
-        <v>56042000</v>
+        <v>-155856000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-64428000</v>
+        <v>985000</v>
       </c>
       <c r="AG3" t="n">
-        <v>64428000</v>
+        <v>-985000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-209975000</v>
+        <v>-114745000</v>
       </c>
       <c r="AI3" t="n">
-        <v>243667000</v>
+        <v>148654000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>33692000</v>
+        <v>33909000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-108226000</v>
+        <v>96544000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1305864000</v>
+        <v>1247235000</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>313236000</v>
+        <v>319550000</v>
       </c>
       <c r="AO3" t="n">
-        <v>992628000</v>
+        <v>927685000</v>
       </c>
       <c r="AP3" t="n">
-        <v>370460000</v>
+        <v>376114000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>622168000</v>
+        <v>551571000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1197638000</v>
+        <v>1343779000</v>
       </c>
       <c r="AS3" t="n">
-        <v>7473371000</v>
+        <v>8040146000</v>
       </c>
       <c r="AT3" t="n">
-        <v>8671009000</v>
+        <v>9383925000</v>
       </c>
       <c r="AU3" t="n">
-        <v>8671009000</v>
+        <v>9383925000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1318750</v>
+        <v>-15821250</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>359559000</v>
+        <v>548875000</v>
       </c>
       <c r="E4" t="n">
-        <v>5275000</v>
+        <v>-63285000</v>
       </c>
       <c r="F4" t="n">
-        <v>5275000</v>
+        <v>-63285000</v>
       </c>
       <c r="G4" t="n">
-        <v>-438462000</v>
+        <v>-269740000</v>
       </c>
       <c r="H4" t="n">
-        <v>530361000</v>
+        <v>505127000</v>
       </c>
       <c r="I4" t="n">
-        <v>8040146000</v>
+        <v>7473371000</v>
       </c>
       <c r="J4" t="n">
-        <v>364834000</v>
+        <v>485590000</v>
       </c>
       <c r="K4" t="n">
-        <v>-165527000</v>
+        <v>-19537000</v>
       </c>
       <c r="L4" t="n">
-        <v>-114745000</v>
+        <v>-209975000</v>
       </c>
       <c r="M4" t="n">
-        <v>148654000</v>
+        <v>243667000</v>
       </c>
       <c r="N4" t="n">
-        <v>33909000</v>
+        <v>33692000</v>
       </c>
       <c r="O4" t="n">
-        <v>-442418250</v>
+        <v>-222276250</v>
       </c>
       <c r="P4" t="n">
-        <v>-438462000</v>
+        <v>-269740000</v>
       </c>
       <c r="Q4" t="n">
-        <v>9287381000</v>
+        <v>8779235000</v>
       </c>
       <c r="R4" t="n">
-        <v>111846985</v>
+        <v>117284677</v>
       </c>
       <c r="S4" t="n">
-        <v>111846985</v>
+        <v>117284677</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.916487</v>
+        <v>-2.295527</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.916487</v>
+        <v>-2.295527</v>
       </c>
       <c r="V4" t="n">
-        <v>-438462000</v>
+        <v>-269740000</v>
       </c>
       <c r="W4" t="n">
-        <v>-438462000</v>
+        <v>-269740000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-438462000</v>
+        <v>-269740000</v>
       </c>
       <c r="Z4" t="n">
-        <v>5913000</v>
+        <v>6601000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-444375000</v>
+        <v>-276341000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-444375000</v>
+        <v>-276341000</v>
       </c>
       <c r="AC4" t="n">
-        <v>130194000</v>
+        <v>13137000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-314181000</v>
+        <v>-263204000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-155856000</v>
+        <v>56042000</v>
       </c>
       <c r="AF4" t="n">
-        <v>985000</v>
+        <v>-64428000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-985000</v>
+        <v>64428000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-114745000</v>
+        <v>-209975000</v>
       </c>
       <c r="AI4" t="n">
-        <v>148654000</v>
+        <v>243667000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>33909000</v>
+        <v>33692000</v>
       </c>
       <c r="AK4" t="n">
-        <v>96544000</v>
+        <v>-108226000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1247235000</v>
+        <v>1305864000</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>319550000</v>
+        <v>313236000</v>
       </c>
       <c r="AO4" t="n">
-        <v>927685000</v>
+        <v>992628000</v>
       </c>
       <c r="AP4" t="n">
-        <v>376114000</v>
+        <v>370460000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>551571000</v>
+        <v>622168000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1343779000</v>
+        <v>1197638000</v>
       </c>
       <c r="AS4" t="n">
-        <v>8040146000</v>
+        <v>7473371000</v>
       </c>
       <c r="AT4" t="n">
-        <v>9383925000</v>
+        <v>8671009000</v>
       </c>
       <c r="AU4" t="n">
-        <v>9383925000</v>
+        <v>8671009000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-2662682.412201</v>
+        <v>-6576000</v>
       </c>
       <c r="C5" t="n">
-        <v>0.332627</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>933194000</v>
+        <v>994431000</v>
       </c>
       <c r="E5" t="n">
-        <v>-8005000</v>
+        <v>-26304000</v>
       </c>
       <c r="F5" t="n">
-        <v>-8005000</v>
+        <v>-26304000</v>
       </c>
       <c r="G5" t="n">
-        <v>216102000</v>
+        <v>-626317000</v>
       </c>
       <c r="H5" t="n">
-        <v>536630000</v>
+        <v>697906000</v>
       </c>
       <c r="I5" t="n">
-        <v>7178390000</v>
+        <v>7253856000</v>
       </c>
       <c r="J5" t="n">
-        <v>925189000</v>
+        <v>968127000</v>
       </c>
       <c r="K5" t="n">
-        <v>388559000</v>
+        <v>270221000</v>
       </c>
       <c r="L5" t="n">
-        <v>-11627000</v>
+        <v>-385953000</v>
       </c>
       <c r="M5" t="n">
-        <v>67939000</v>
+        <v>432581000</v>
       </c>
       <c r="N5" t="n">
-        <v>56312000</v>
+        <v>46628000</v>
       </c>
       <c r="O5" t="n">
-        <v>221444317.587799</v>
+        <v>-606589000</v>
       </c>
       <c r="P5" t="n">
-        <v>216102000</v>
+        <v>-626317000</v>
       </c>
       <c r="Q5" t="n">
-        <v>8625701000</v>
+        <v>8377012000</v>
       </c>
       <c r="R5" t="n">
-        <v>127533348</v>
+        <v>121087000</v>
       </c>
       <c r="S5" t="n">
-        <v>111846985</v>
+        <v>121087000</v>
       </c>
       <c r="T5" t="n">
-        <v>1.859342</v>
+        <v>-5.17</v>
       </c>
       <c r="U5" t="n">
-        <v>1.928573</v>
+        <v>-5.17</v>
       </c>
       <c r="V5" t="n">
-        <v>216102000</v>
+        <v>-626317000</v>
       </c>
       <c r="W5" t="n">
-        <v>216102000</v>
+        <v>-626317000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>216102000</v>
+        <v>-626317000</v>
       </c>
       <c r="Z5" t="n">
-        <v>2129000</v>
+        <v>6972000</v>
       </c>
       <c r="AA5" t="n">
-        <v>213973000</v>
+        <v>-633289000</v>
       </c>
       <c r="AB5" t="n">
-        <v>213973000</v>
+        <v>-633289000</v>
       </c>
       <c r="AC5" t="n">
-        <v>106647000</v>
+        <v>470929000</v>
       </c>
       <c r="AD5" t="n">
-        <v>320620000</v>
+        <v>-162360000</v>
       </c>
       <c r="AE5" t="n">
-        <v>14348000</v>
+        <v>1526023000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-6453000</v>
+        <v>-4685000</v>
       </c>
       <c r="AG5" t="n">
-        <v>6453000</v>
+        <v>4685000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-11627000</v>
+        <v>-385953000</v>
       </c>
       <c r="AI5" t="n">
-        <v>67939000</v>
+        <v>432581000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>56312000</v>
+        <v>46628000</v>
       </c>
       <c r="AK5" t="n">
-        <v>322510000</v>
+        <v>-1174776000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1447311000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>6453000</v>
-      </c>
+        <v>1123156000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>351541000</v>
+        <v>227037000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1095770000</v>
+        <v>896119000</v>
       </c>
       <c r="AP5" t="n">
-        <v>476495000</v>
+        <v>371847000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>619275000</v>
+        <v>524272000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1769821000</v>
+        <v>-51620000</v>
       </c>
       <c r="AS5" t="n">
-        <v>7178390000</v>
+        <v>7253856000</v>
       </c>
       <c r="AT5" t="n">
-        <v>8948211000</v>
+        <v>7202236000</v>
       </c>
       <c r="AU5" t="n">
-        <v>8948211000</v>
+        <v>7202236000</v>
       </c>
     </row>
   </sheetData>
@@ -1524,696 +1524,696 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>133135941</v>
+        <v>111846985</v>
       </c>
       <c r="C2" t="n">
-        <v>133135941</v>
+        <v>111846985</v>
       </c>
       <c r="D2" t="n">
-        <v>11568293000</v>
+        <v>5849683000</v>
       </c>
       <c r="E2" t="n">
-        <v>14472066000</v>
+        <v>8048391000</v>
       </c>
       <c r="F2" t="n">
-        <v>8840553000</v>
+        <v>8571312000</v>
       </c>
       <c r="G2" t="n">
-        <v>23243444000</v>
+        <v>16552726000</v>
       </c>
       <c r="H2" t="n">
-        <v>2098339000</v>
+        <v>3861211000</v>
       </c>
       <c r="I2" t="n">
-        <v>8840553000</v>
+        <v>8571312000</v>
       </c>
       <c r="J2" t="n">
-        <v>209877000</v>
+        <v>204935000</v>
       </c>
       <c r="K2" t="n">
-        <v>8981255000</v>
+        <v>8709270000</v>
       </c>
       <c r="L2" t="n">
-        <v>17256453000</v>
+        <v>12687046000</v>
       </c>
       <c r="M2" t="n">
-        <v>9300196000</v>
+        <v>8834615000</v>
       </c>
       <c r="N2" t="n">
-        <v>318941000</v>
+        <v>125345000</v>
       </c>
       <c r="O2" t="n">
-        <v>8981255000</v>
+        <v>8709270000</v>
       </c>
       <c r="P2" t="n">
-        <v>-317750000</v>
+        <v>1023039000</v>
       </c>
       <c r="Q2" t="n">
-        <v>6940472000</v>
+        <v>5980154000</v>
       </c>
       <c r="R2" t="n">
-        <v>1331359000</v>
+        <v>1106175000</v>
       </c>
       <c r="S2" t="n">
-        <v>1331359000</v>
+        <v>1106175000</v>
       </c>
       <c r="T2" t="n">
-        <v>16461930000</v>
+        <v>9635241000</v>
       </c>
       <c r="U2" t="n">
-        <v>8732122000</v>
+        <v>4191396000</v>
       </c>
       <c r="V2" t="n">
-        <v>236243000</v>
+        <v>7966000</v>
       </c>
       <c r="W2" t="n">
-        <v>8462249000</v>
+        <v>4158680000</v>
       </c>
       <c r="X2" t="n">
-        <v>187051000</v>
+        <v>180904000</v>
       </c>
       <c r="Y2" t="n">
-        <v>8275198000</v>
+        <v>3977776000</v>
       </c>
       <c r="Z2" t="n">
-        <v>7729808000</v>
+        <v>5443845000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1773000</v>
+        <v>12202000</v>
       </c>
       <c r="AB2" t="n">
-        <v>6009817000</v>
+        <v>3889711000</v>
       </c>
       <c r="AC2" t="n">
-        <v>22826000</v>
+        <v>24031000</v>
       </c>
       <c r="AD2" t="n">
-        <v>5986991000</v>
+        <v>3865680000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1708322000</v>
+        <v>1541932000</v>
       </c>
       <c r="AF2" t="n">
-        <v>895005000</v>
+        <v>687750000</v>
       </c>
       <c r="AG2" t="n">
-        <v>19039000</v>
+        <v>67513000</v>
       </c>
       <c r="AH2" t="n">
-        <v>794278000</v>
+        <v>786669000</v>
       </c>
       <c r="AI2" t="n">
-        <v>25762126000</v>
+        <v>18469856000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>15933979000</v>
+        <v>9164800000</v>
       </c>
       <c r="AK2" t="n">
-        <v>140495000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>43397000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>865754000</v>
+      </c>
       <c r="AM2" t="n">
-        <v>107474000</v>
+        <v>67025000</v>
       </c>
       <c r="AN2" t="n">
-        <v>193906000</v>
+        <v>246911000</v>
       </c>
       <c r="AO2" t="n">
-        <v>193906000</v>
+        <v>246911000</v>
       </c>
       <c r="AP2" t="n">
-        <v>712000</v>
+        <v>731000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>140702000</v>
+        <v>137958000</v>
       </c>
       <c r="AR2" t="n">
-        <v>140702000</v>
+        <v>137958000</v>
       </c>
       <c r="AS2" t="n">
-        <v>15350690000</v>
+        <v>8668778000</v>
       </c>
       <c r="AT2" t="n">
-        <v>15350690000</v>
+        <v>8668778000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1252304000</v>
+        <v>724498000</v>
       </c>
       <c r="AV2" t="n">
-        <v>14098386000</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>7803024000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>141256000</v>
+      </c>
       <c r="AX2" t="n">
-        <v>9828147000</v>
+        <v>9305056000</v>
       </c>
       <c r="AY2" t="n">
-        <v>1368326000</v>
+        <v>418575000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1636040000</v>
+        <v>1660444000</v>
       </c>
       <c r="BA2" t="n">
-        <v>371669000</v>
+        <v>432953000</v>
       </c>
       <c r="BB2" t="n">
-        <v>2751723000</v>
+        <v>2808556000</v>
       </c>
       <c r="BC2" t="n">
-        <v>2751723000</v>
+        <v>2808556000</v>
       </c>
       <c r="BD2" t="n">
-        <v>3700389000</v>
+        <v>3984528000</v>
       </c>
       <c r="BE2" t="n">
-        <v>1006493000</v>
+        <v>1990755000</v>
       </c>
       <c r="BF2" t="n">
-        <v>2693896000</v>
+        <v>1993773000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>119448511</v>
+        <v>111846985</v>
       </c>
       <c r="C3" t="n">
-        <v>119448511</v>
+        <v>111846985</v>
       </c>
       <c r="D3" t="n">
-        <v>12443761000</v>
+        <v>9197899000</v>
       </c>
       <c r="E3" t="n">
-        <v>14858382000</v>
+        <v>11499297000</v>
       </c>
       <c r="F3" t="n">
-        <v>8422163000</v>
+        <v>8225110000</v>
       </c>
       <c r="G3" t="n">
-        <v>23200355000</v>
+        <v>19676230000</v>
       </c>
       <c r="H3" t="n">
-        <v>2718693000</v>
+        <v>1548462000</v>
       </c>
       <c r="I3" t="n">
-        <v>8422163000</v>
+        <v>8225110000</v>
       </c>
       <c r="J3" t="n">
-        <v>218078000</v>
+        <v>187018000</v>
       </c>
       <c r="K3" t="n">
-        <v>8560051000</v>
+        <v>8363951000</v>
       </c>
       <c r="L3" t="n">
-        <v>17330749000</v>
+        <v>13463922000</v>
       </c>
       <c r="M3" t="n">
-        <v>8727368000</v>
+        <v>8492012000</v>
       </c>
       <c r="N3" t="n">
-        <v>167317000</v>
+        <v>128061000</v>
       </c>
       <c r="O3" t="n">
-        <v>8560051000</v>
+        <v>8363951000</v>
       </c>
       <c r="P3" t="n">
-        <v>503002000</v>
+        <v>544916000</v>
       </c>
       <c r="Q3" t="n">
-        <v>6490466000</v>
+        <v>5980154000</v>
       </c>
       <c r="R3" t="n">
-        <v>1181359000</v>
+        <v>1106175000</v>
       </c>
       <c r="S3" t="n">
-        <v>1181359000</v>
+        <v>1106175000</v>
       </c>
       <c r="T3" t="n">
-        <v>16349138000</v>
+        <v>13398907000</v>
       </c>
       <c r="U3" t="n">
-        <v>8988130000</v>
+        <v>5280797000</v>
       </c>
       <c r="V3" t="n">
-        <v>5648000</v>
+        <v>9391000</v>
       </c>
       <c r="W3" t="n">
-        <v>8970309000</v>
+        <v>5271406000</v>
       </c>
       <c r="X3" t="n">
-        <v>199611000</v>
+        <v>171435000</v>
       </c>
       <c r="Y3" t="n">
-        <v>8770698000</v>
+        <v>5099971000</v>
       </c>
       <c r="Z3" t="n">
-        <v>7361008000</v>
+        <v>8118110000</v>
       </c>
       <c r="AA3" t="n">
-        <v>2988000</v>
+        <v>17159000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5888073000</v>
+        <v>6227891000</v>
       </c>
       <c r="AC3" t="n">
-        <v>18467000</v>
+        <v>15583000</v>
       </c>
       <c r="AD3" t="n">
-        <v>5869606000</v>
+        <v>6212308000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1456657000</v>
+        <v>1834676000</v>
       </c>
       <c r="AF3" t="n">
-        <v>793967000</v>
+        <v>850442000</v>
       </c>
       <c r="AG3" t="n">
-        <v>27130000</v>
+        <v>38298000</v>
       </c>
       <c r="AH3" t="n">
-        <v>635560000</v>
+        <v>945936000</v>
       </c>
       <c r="AI3" t="n">
-        <v>25076506000</v>
+        <v>21890919000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14996805000</v>
+        <v>12224347000</v>
       </c>
       <c r="AK3" t="n">
-        <v>67088000</v>
+        <v>46172000</v>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>133879000</v>
+        <v>88258000</v>
       </c>
       <c r="AN3" t="n">
-        <v>168534000</v>
+        <v>98623000</v>
       </c>
       <c r="AO3" t="n">
-        <v>168534000</v>
+        <v>98623000</v>
       </c>
       <c r="AP3" t="n">
-        <v>719000</v>
+        <v>725000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>137888000</v>
+        <v>138841000</v>
       </c>
       <c r="AR3" t="n">
-        <v>137888000</v>
+        <v>138841000</v>
       </c>
       <c r="AS3" t="n">
-        <v>14488697000</v>
+        <v>11851728000</v>
       </c>
       <c r="AT3" t="n">
-        <v>14488697000</v>
+        <v>11851728000</v>
       </c>
       <c r="AU3" t="n">
-        <v>2183512000</v>
+        <v>1660088000</v>
       </c>
       <c r="AV3" t="n">
-        <v>12305185000</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>10191640000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
       <c r="AX3" t="n">
-        <v>10079701000</v>
+        <v>9666572000</v>
       </c>
       <c r="AY3" t="n">
-        <v>572533000</v>
+        <v>514377000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2325047000</v>
+        <v>1858470000</v>
       </c>
       <c r="BA3" t="n">
-        <v>609795000</v>
+        <v>302372000</v>
       </c>
       <c r="BB3" t="n">
-        <v>2754519000</v>
+        <v>3440286000</v>
       </c>
       <c r="BC3" t="n">
-        <v>2754519000</v>
+        <v>3440286000</v>
       </c>
       <c r="BD3" t="n">
-        <v>3817807000</v>
+        <v>3551067000</v>
       </c>
       <c r="BE3" t="n">
-        <v>1621264000</v>
+        <v>1436687000</v>
       </c>
       <c r="BF3" t="n">
-        <v>2196543000</v>
+        <v>2114380000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>111846985</v>
+        <v>119448511</v>
       </c>
       <c r="C4" t="n">
-        <v>111846985</v>
+        <v>119448511</v>
       </c>
       <c r="D4" t="n">
-        <v>9197899000</v>
+        <v>12443761000</v>
       </c>
       <c r="E4" t="n">
-        <v>11499297000</v>
+        <v>14858382000</v>
       </c>
       <c r="F4" t="n">
-        <v>8225110000</v>
+        <v>8422163000</v>
       </c>
       <c r="G4" t="n">
-        <v>19676230000</v>
+        <v>23200355000</v>
       </c>
       <c r="H4" t="n">
-        <v>1548462000</v>
+        <v>2718693000</v>
       </c>
       <c r="I4" t="n">
-        <v>8225110000</v>
+        <v>8422163000</v>
       </c>
       <c r="J4" t="n">
-        <v>187018000</v>
+        <v>218078000</v>
       </c>
       <c r="K4" t="n">
-        <v>8363951000</v>
+        <v>8560051000</v>
       </c>
       <c r="L4" t="n">
-        <v>13463922000</v>
+        <v>17330749000</v>
       </c>
       <c r="M4" t="n">
-        <v>8492012000</v>
+        <v>8727368000</v>
       </c>
       <c r="N4" t="n">
-        <v>128061000</v>
+        <v>167317000</v>
       </c>
       <c r="O4" t="n">
-        <v>8363951000</v>
+        <v>8560051000</v>
       </c>
       <c r="P4" t="n">
-        <v>544916000</v>
+        <v>503002000</v>
       </c>
       <c r="Q4" t="n">
-        <v>5980154000</v>
+        <v>6490466000</v>
       </c>
       <c r="R4" t="n">
-        <v>1106175000</v>
+        <v>1181359000</v>
       </c>
       <c r="S4" t="n">
-        <v>1106175000</v>
+        <v>1181359000</v>
       </c>
       <c r="T4" t="n">
-        <v>13398907000</v>
+        <v>16349138000</v>
       </c>
       <c r="U4" t="n">
-        <v>5280797000</v>
+        <v>8988130000</v>
       </c>
       <c r="V4" t="n">
-        <v>9391000</v>
+        <v>5648000</v>
       </c>
       <c r="W4" t="n">
-        <v>5271406000</v>
+        <v>8970309000</v>
       </c>
       <c r="X4" t="n">
-        <v>171435000</v>
+        <v>199611000</v>
       </c>
       <c r="Y4" t="n">
-        <v>5099971000</v>
+        <v>8770698000</v>
       </c>
       <c r="Z4" t="n">
-        <v>8118110000</v>
+        <v>7361008000</v>
       </c>
       <c r="AA4" t="n">
-        <v>17159000</v>
+        <v>2988000</v>
       </c>
       <c r="AB4" t="n">
-        <v>6227891000</v>
+        <v>5888073000</v>
       </c>
       <c r="AC4" t="n">
-        <v>15583000</v>
+        <v>18467000</v>
       </c>
       <c r="AD4" t="n">
-        <v>6212308000</v>
+        <v>5869606000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1834676000</v>
+        <v>1456657000</v>
       </c>
       <c r="AF4" t="n">
-        <v>850442000</v>
+        <v>793967000</v>
       </c>
       <c r="AG4" t="n">
-        <v>38298000</v>
+        <v>27130000</v>
       </c>
       <c r="AH4" t="n">
-        <v>945936000</v>
+        <v>635560000</v>
       </c>
       <c r="AI4" t="n">
-        <v>21890919000</v>
+        <v>25076506000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12224347000</v>
+        <v>14996805000</v>
       </c>
       <c r="AK4" t="n">
-        <v>46172000</v>
+        <v>67088000</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>88258000</v>
+        <v>133879000</v>
       </c>
       <c r="AN4" t="n">
-        <v>98623000</v>
+        <v>168534000</v>
       </c>
       <c r="AO4" t="n">
-        <v>98623000</v>
+        <v>168534000</v>
       </c>
       <c r="AP4" t="n">
-        <v>725000</v>
+        <v>719000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>138841000</v>
+        <v>137888000</v>
       </c>
       <c r="AR4" t="n">
-        <v>138841000</v>
+        <v>137888000</v>
       </c>
       <c r="AS4" t="n">
-        <v>11851728000</v>
+        <v>14488697000</v>
       </c>
       <c r="AT4" t="n">
-        <v>11851728000</v>
+        <v>14488697000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1660088000</v>
+        <v>2183512000</v>
       </c>
       <c r="AV4" t="n">
-        <v>10191640000</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
+        <v>12305185000</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>9666572000</v>
+        <v>10079701000</v>
       </c>
       <c r="AY4" t="n">
-        <v>514377000</v>
+        <v>572533000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1858470000</v>
+        <v>2325047000</v>
       </c>
       <c r="BA4" t="n">
-        <v>302372000</v>
+        <v>609795000</v>
       </c>
       <c r="BB4" t="n">
-        <v>3440286000</v>
+        <v>2754519000</v>
       </c>
       <c r="BC4" t="n">
-        <v>3440286000</v>
+        <v>2754519000</v>
       </c>
       <c r="BD4" t="n">
-        <v>3551067000</v>
+        <v>3817807000</v>
       </c>
       <c r="BE4" t="n">
-        <v>1436687000</v>
+        <v>1621264000</v>
       </c>
       <c r="BF4" t="n">
-        <v>2114380000</v>
+        <v>2196543000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>111846985</v>
+        <v>133135941</v>
       </c>
       <c r="C5" t="n">
-        <v>111846985</v>
+        <v>133135941</v>
       </c>
       <c r="D5" t="n">
-        <v>5849683000</v>
+        <v>11568293000</v>
       </c>
       <c r="E5" t="n">
-        <v>8048391000</v>
+        <v>14472066000</v>
       </c>
       <c r="F5" t="n">
-        <v>8571312000</v>
+        <v>8840553000</v>
       </c>
       <c r="G5" t="n">
-        <v>16552726000</v>
+        <v>23243444000</v>
       </c>
       <c r="H5" t="n">
-        <v>3861211000</v>
+        <v>2098339000</v>
       </c>
       <c r="I5" t="n">
-        <v>8571312000</v>
+        <v>8840553000</v>
       </c>
       <c r="J5" t="n">
-        <v>204935000</v>
+        <v>209877000</v>
       </c>
       <c r="K5" t="n">
-        <v>8709270000</v>
+        <v>8981255000</v>
       </c>
       <c r="L5" t="n">
-        <v>12687046000</v>
+        <v>17256453000</v>
       </c>
       <c r="M5" t="n">
-        <v>8834615000</v>
+        <v>9300196000</v>
       </c>
       <c r="N5" t="n">
-        <v>125345000</v>
+        <v>318941000</v>
       </c>
       <c r="O5" t="n">
-        <v>8709270000</v>
+        <v>8981255000</v>
       </c>
       <c r="P5" t="n">
-        <v>1023039000</v>
+        <v>-317750000</v>
       </c>
       <c r="Q5" t="n">
-        <v>5980154000</v>
+        <v>6940472000</v>
       </c>
       <c r="R5" t="n">
-        <v>1106175000</v>
+        <v>1331359000</v>
       </c>
       <c r="S5" t="n">
-        <v>1106175000</v>
+        <v>1331359000</v>
       </c>
       <c r="T5" t="n">
-        <v>9635241000</v>
+        <v>16461930000</v>
       </c>
       <c r="U5" t="n">
-        <v>4191396000</v>
+        <v>8732122000</v>
       </c>
       <c r="V5" t="n">
-        <v>7966000</v>
+        <v>236243000</v>
       </c>
       <c r="W5" t="n">
-        <v>4158680000</v>
+        <v>8462249000</v>
       </c>
       <c r="X5" t="n">
-        <v>180904000</v>
+        <v>187051000</v>
       </c>
       <c r="Y5" t="n">
-        <v>3977776000</v>
+        <v>8275198000</v>
       </c>
       <c r="Z5" t="n">
-        <v>5443845000</v>
+        <v>7729808000</v>
       </c>
       <c r="AA5" t="n">
-        <v>12202000</v>
+        <v>1773000</v>
       </c>
       <c r="AB5" t="n">
-        <v>3889711000</v>
+        <v>6009817000</v>
       </c>
       <c r="AC5" t="n">
-        <v>24031000</v>
+        <v>22826000</v>
       </c>
       <c r="AD5" t="n">
-        <v>3865680000</v>
+        <v>5986991000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1541932000</v>
+        <v>1708322000</v>
       </c>
       <c r="AF5" t="n">
-        <v>687750000</v>
+        <v>895005000</v>
       </c>
       <c r="AG5" t="n">
-        <v>67513000</v>
+        <v>19039000</v>
       </c>
       <c r="AH5" t="n">
-        <v>786669000</v>
+        <v>794278000</v>
       </c>
       <c r="AI5" t="n">
-        <v>18469856000</v>
+        <v>25762126000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9164800000</v>
+        <v>15933979000</v>
       </c>
       <c r="AK5" t="n">
-        <v>43397000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>865754000</v>
-      </c>
+        <v>140495000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>67025000</v>
+        <v>107474000</v>
       </c>
       <c r="AN5" t="n">
-        <v>246911000</v>
+        <v>193906000</v>
       </c>
       <c r="AO5" t="n">
-        <v>246911000</v>
+        <v>193906000</v>
       </c>
       <c r="AP5" t="n">
-        <v>731000</v>
+        <v>712000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>137958000</v>
+        <v>140702000</v>
       </c>
       <c r="AR5" t="n">
-        <v>137958000</v>
+        <v>140702000</v>
       </c>
       <c r="AS5" t="n">
-        <v>8668778000</v>
+        <v>15350690000</v>
       </c>
       <c r="AT5" t="n">
-        <v>8668778000</v>
+        <v>15350690000</v>
       </c>
       <c r="AU5" t="n">
-        <v>724498000</v>
+        <v>1252304000</v>
       </c>
       <c r="AV5" t="n">
-        <v>7803024000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>141256000</v>
-      </c>
+        <v>14098386000</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>9305056000</v>
+        <v>9828147000</v>
       </c>
       <c r="AY5" t="n">
-        <v>418575000</v>
+        <v>1368326000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1660444000</v>
+        <v>1636040000</v>
       </c>
       <c r="BA5" t="n">
-        <v>432953000</v>
+        <v>371669000</v>
       </c>
       <c r="BB5" t="n">
-        <v>2808556000</v>
+        <v>2751723000</v>
       </c>
       <c r="BC5" t="n">
-        <v>2808556000</v>
+        <v>2751723000</v>
       </c>
       <c r="BD5" t="n">
-        <v>3984528000</v>
+        <v>3700389000</v>
       </c>
       <c r="BE5" t="n">
-        <v>1990755000</v>
+        <v>1006493000</v>
       </c>
       <c r="BF5" t="n">
-        <v>1993773000</v>
+        <v>2693896000</v>
       </c>
     </row>
   </sheetData>
@@ -2494,620 +2494,620 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-1403933000</v>
+        <v>-1459952000</v>
       </c>
       <c r="C2" t="n">
-        <v>-503783000</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>811050000</v>
+        <v>1240236000</v>
       </c>
       <c r="E2" t="n">
-        <v>600000000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-1128566000</v>
+        <v>-2455512000</v>
       </c>
       <c r="G2" t="n">
-        <v>2693896000</v>
+        <v>1993773000</v>
       </c>
       <c r="H2" t="n">
-        <v>2196543000</v>
+        <v>2682852000</v>
       </c>
       <c r="I2" t="n">
-        <v>-244731000</v>
+        <v>40076000</v>
       </c>
       <c r="J2" t="n">
-        <v>742084000</v>
+        <v>-729155000</v>
       </c>
       <c r="K2" t="n">
-        <v>1013573000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>140710000</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
+        <v>1033036000</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>-165926000</v>
+      </c>
       <c r="N2" t="n">
-        <v>600000000</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>600000000</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>307267000</v>
+        <v>1240236000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-503783000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-503783000</v>
-      </c>
+        <v>652009000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>652009000</v>
       </c>
       <c r="T2" t="n">
-        <v>811050000</v>
+        <v>588227000</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>811050000</v>
+        <v>588227000</v>
       </c>
       <c r="W2" t="n">
-        <v>3878000</v>
+        <v>-2757751000</v>
       </c>
       <c r="X2" t="n">
-        <v>432747000</v>
+        <v>-144879000</v>
       </c>
       <c r="Y2" t="n">
-        <v>46068000</v>
+        <v>56118000</v>
       </c>
       <c r="Z2" t="n">
-        <v>371102000</v>
+        <v>-186262000</v>
       </c>
       <c r="AA2" t="n">
-        <v>475093000</v>
+        <v>839763000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-103991000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+        <v>-1026025000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-30836000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-30836000</v>
+      </c>
       <c r="AE2" t="n">
-        <v>-12788000</v>
+        <v>-2995000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-12788000</v>
+        <v>-2995000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-833251000</v>
+        <v>-2448897000</v>
       </c>
       <c r="AH2" t="n">
-        <v>282527000</v>
+        <v>3620000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1115778000</v>
+        <v>-2452517000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-275367000</v>
+        <v>995560000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-220196000</v>
+        <v>-8669000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-429921000</v>
+        <v>-65905000</v>
       </c>
       <c r="AM2" t="n">
-        <v>615670000</v>
+        <v>147625000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-758407000</v>
+        <v>416204000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-90542000</v>
+        <v>-161409000</v>
       </c>
       <c r="AP2" t="n">
-        <v>192543000</v>
+        <v>-64228000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>861577000</v>
+        <v>-331366000</v>
       </c>
       <c r="AR2" t="n">
-        <v>410499000</v>
+        <v>288424000</v>
       </c>
       <c r="AS2" t="n">
-        <v>385953000</v>
+        <v>11378000</v>
       </c>
       <c r="AT2" t="n">
-        <v>4685000</v>
+        <v>6453000</v>
       </c>
       <c r="AU2" t="n">
-        <v>697906000</v>
+        <v>536630000</v>
       </c>
       <c r="AV2" t="n">
-        <v>6459000</v>
+        <v>6176000</v>
       </c>
       <c r="AW2" t="n">
-        <v>691447000</v>
+        <v>530454000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-397684000</v>
+        <v>20916000</v>
       </c>
       <c r="AY2" t="n">
-        <v>42728000</v>
+        <v>-8311000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-751918000</v>
+        <v>27305000</v>
       </c>
       <c r="BA2" t="n">
-        <v>-162360000</v>
+        <v>320620000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-3579909000</v>
+        <v>-3991993000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1422358000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>5350632000</v>
-      </c>
-      <c r="E3" t="n">
+        <v>3448174000</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>-3692485000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2114380000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1993773000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>35592000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>85015000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3349419000</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>-66371000</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>3448174000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1466140000</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>1466140000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1982034000</v>
+      </c>
+      <c r="U3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
-        <v>-3084155000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2196543000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2114380000</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-52526000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>134689000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3944930000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>44640000</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
+      <c r="V3" t="n">
+        <v>1982034000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-2964896000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-3340000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>34536000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>691330000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>750972000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-59642000</v>
+      </c>
+      <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
+      <c r="AD3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
-        <v>3928274000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1160973000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1160973000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2767301000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-1422358000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>4189659000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-3314487000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-8950000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>33014000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-271603000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>409540000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-681143000</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>-1149000</v>
+        <v>-7662000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1149000</v>
+        <v>-7662000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-3065799000</v>
+        <v>-3679760000</v>
       </c>
       <c r="AH3" t="n">
-        <v>17207000</v>
+        <v>5063000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-3083006000</v>
+        <v>-3684823000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-495754000</v>
+        <v>-299508000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-75544000</v>
+        <v>-179513000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-333248000</v>
+        <v>-158706000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-706361000</v>
+        <v>-762110000</v>
       </c>
       <c r="AN3" t="n">
-        <v>116887000</v>
+        <v>-270355000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-91913000</v>
+        <v>-89792000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-331523000</v>
+        <v>233541000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-643950000</v>
+        <v>-189994000</v>
       </c>
       <c r="AR3" t="n">
-        <v>244138000</v>
+        <v>-445510000</v>
       </c>
       <c r="AS3" t="n">
-        <v>209975000</v>
+        <v>114739000</v>
       </c>
       <c r="AT3" t="n">
-        <v>64428000</v>
+        <v>-985000</v>
       </c>
       <c r="AU3" t="n">
-        <v>505127000</v>
+        <v>530361000</v>
       </c>
       <c r="AV3" t="n">
-        <v>7413000</v>
+        <v>8927000</v>
       </c>
       <c r="AW3" t="n">
-        <v>497714000</v>
+        <v>521434000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-1143000</v>
+        <v>2599000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-35333000</v>
+        <v>271165000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9784000</v>
+        <v>89266000</v>
       </c>
       <c r="BA3" t="n">
-        <v>-263204000</v>
+        <v>-314181000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-3991993000</v>
+        <v>-3579909000</v>
       </c>
       <c r="C4" t="n">
+        <v>-1422358000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5350632000</v>
+      </c>
+      <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
-        <v>3448174000</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-3692485000</v>
+        <v>-3084155000</v>
       </c>
       <c r="G4" t="n">
+        <v>2196543000</v>
+      </c>
+      <c r="H4" t="n">
         <v>2114380000</v>
       </c>
-      <c r="H4" t="n">
-        <v>1993773000</v>
-      </c>
       <c r="I4" t="n">
-        <v>35592000</v>
+        <v>-52526000</v>
       </c>
       <c r="J4" t="n">
-        <v>85015000</v>
+        <v>134689000</v>
       </c>
       <c r="K4" t="n">
-        <v>3349419000</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>-66371000</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+        <v>3944930000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>44640000</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
-        <v>3448174000</v>
+        <v>3928274000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1466140000</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>1160973000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
       <c r="S4" t="n">
-        <v>1466140000</v>
+        <v>1160973000</v>
       </c>
       <c r="T4" t="n">
-        <v>1982034000</v>
+        <v>2767301000</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-1422358000</v>
       </c>
       <c r="V4" t="n">
-        <v>1982034000</v>
+        <v>4189659000</v>
       </c>
       <c r="W4" t="n">
-        <v>-2964896000</v>
+        <v>-3314487000</v>
       </c>
       <c r="X4" t="n">
-        <v>-3340000</v>
+        <v>-8950000</v>
       </c>
       <c r="Y4" t="n">
-        <v>34536000</v>
+        <v>33014000</v>
       </c>
       <c r="Z4" t="n">
-        <v>691330000</v>
+        <v>-271603000</v>
       </c>
       <c r="AA4" t="n">
-        <v>750972000</v>
+        <v>409540000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-59642000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
+        <v>-681143000</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>-7662000</v>
+        <v>-1149000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-7662000</v>
+        <v>-1149000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3679760000</v>
+        <v>-3065799000</v>
       </c>
       <c r="AH4" t="n">
-        <v>5063000</v>
+        <v>17207000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-3684823000</v>
+        <v>-3083006000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-299508000</v>
+        <v>-495754000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-179513000</v>
+        <v>-75544000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-158706000</v>
+        <v>-333248000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-762110000</v>
+        <v>-706361000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-270355000</v>
+        <v>116887000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-89792000</v>
+        <v>-91913000</v>
       </c>
       <c r="AP4" t="n">
-        <v>233541000</v>
+        <v>-331523000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-189994000</v>
+        <v>-643950000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-445510000</v>
+        <v>244138000</v>
       </c>
       <c r="AS4" t="n">
-        <v>114739000</v>
+        <v>209975000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-985000</v>
+        <v>64428000</v>
       </c>
       <c r="AU4" t="n">
-        <v>530361000</v>
+        <v>505127000</v>
       </c>
       <c r="AV4" t="n">
-        <v>8927000</v>
+        <v>7413000</v>
       </c>
       <c r="AW4" t="n">
-        <v>521434000</v>
+        <v>497714000</v>
       </c>
       <c r="AX4" t="n">
-        <v>2599000</v>
+        <v>-1143000</v>
       </c>
       <c r="AY4" t="n">
-        <v>271165000</v>
+        <v>-35333000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>89266000</v>
+        <v>9784000</v>
       </c>
       <c r="BA4" t="n">
-        <v>-314181000</v>
+        <v>-263204000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1459952000</v>
+        <v>-1403933000</v>
       </c>
       <c r="C5" t="n">
+        <v>-503783000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>811050000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>600000000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1128566000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2693896000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2196543000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-244731000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>742084000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1013573000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>140710000</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>600000000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>600000000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>307267000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-503783000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-503783000</v>
+      </c>
+      <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="n">
-        <v>1240236000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-2455512000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1993773000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2682852000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>40076000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-729155000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1033036000</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>-165926000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1240236000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>652009000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>652009000</v>
-      </c>
       <c r="T5" t="n">
-        <v>588227000</v>
+        <v>811050000</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>588227000</v>
+        <v>811050000</v>
       </c>
       <c r="W5" t="n">
-        <v>-2757751000</v>
+        <v>3878000</v>
       </c>
       <c r="X5" t="n">
-        <v>-144879000</v>
+        <v>432747000</v>
       </c>
       <c r="Y5" t="n">
-        <v>56118000</v>
+        <v>46068000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-186262000</v>
+        <v>371102000</v>
       </c>
       <c r="AA5" t="n">
-        <v>839763000</v>
+        <v>475093000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1026025000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-30836000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-30836000</v>
-      </c>
+        <v>-103991000</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>-2995000</v>
+        <v>-12788000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-2995000</v>
+        <v>-12788000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-2448897000</v>
+        <v>-833251000</v>
       </c>
       <c r="AH5" t="n">
-        <v>3620000</v>
+        <v>282527000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2452517000</v>
+        <v>-1115778000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>995560000</v>
+        <v>-275367000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-8669000</v>
+        <v>-220196000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-65905000</v>
+        <v>-429921000</v>
       </c>
       <c r="AM5" t="n">
-        <v>147625000</v>
+        <v>615670000</v>
       </c>
       <c r="AN5" t="n">
-        <v>416204000</v>
+        <v>-758407000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-161409000</v>
+        <v>-90542000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-64228000</v>
+        <v>192543000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-331366000</v>
+        <v>861577000</v>
       </c>
       <c r="AR5" t="n">
-        <v>288424000</v>
+        <v>410499000</v>
       </c>
       <c r="AS5" t="n">
-        <v>11378000</v>
+        <v>385953000</v>
       </c>
       <c r="AT5" t="n">
-        <v>6453000</v>
+        <v>4685000</v>
       </c>
       <c r="AU5" t="n">
-        <v>536630000</v>
+        <v>697906000</v>
       </c>
       <c r="AV5" t="n">
-        <v>6176000</v>
+        <v>6459000</v>
       </c>
       <c r="AW5" t="n">
-        <v>530454000</v>
+        <v>691447000</v>
       </c>
       <c r="AX5" t="n">
-        <v>20916000</v>
+        <v>-397684000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-8311000</v>
+        <v>42728000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>27305000</v>
+        <v>-751918000</v>
       </c>
       <c r="BA5" t="n">
-        <v>320620000</v>
+        <v>-162360000</v>
       </c>
     </row>
   </sheetData>
@@ -3647,192 +3647,192 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>shortName</t>
         </is>
       </c>
       <c r="EM1" t="inlineStr">
@@ -3957,7 +3957,7 @@
         <v>3.96</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AD2" t="n">
         <v>1.2122538</v>
@@ -3969,7 +3969,7 @@
         <v>8432214</v>
       </c>
       <c r="AG2" t="n">
-        <v>684725</v>
+        <v>244413</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -3999,7 +3999,7 @@
         <v>5.54</v>
       </c>
       <c r="AQ2" t="n">
-        <v>27.35</v>
+        <v>26</v>
       </c>
       <c r="AR2" t="n">
         <v>245.49658</v>
@@ -4011,10 +4011,10 @@
         <v>0.105496734</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.8492</v>
+        <v>5.54</v>
       </c>
       <c r="AV2" t="n">
-        <v>14.892826</v>
+        <v>13.719626</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
         <v>0.24497</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0110599995</v>
+        <v>0.0111</v>
       </c>
       <c r="BG2" t="n">
         <v>153135941</v>
@@ -4090,10 +4090,10 @@
         <v>1043.682</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.78692305</v>
+        <v>-0.7642553</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="n">
         <v>0.5796519999999999</v>
@@ -4206,143 +4206,143 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DA2" t="b">
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>TAI</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>finmb_59505315</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>Asia/Taipei</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>tw_market</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
         <v>0</v>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-8.179626000000001</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.5961989</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>1775107808</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>YEONG GUAN ENERGY TECHNOLOGY GP</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
         <is>
           <t>Yeong Guan Energy Technology Group Co., Ltd.</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>TAI</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>finmb_59505315</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>Asia/Taipei</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="DG2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>tw_market</t>
-        </is>
-      </c>
-      <c r="DI2" t="b">
+      <c r="DT2" t="b">
         <v>0</v>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DU2" t="n">
+        <v>1335488400000</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>5.54 - 5.54</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>244413</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>5.54 - 26.0</t>
+        </is>
+      </c>
+      <c r="EC2" t="n">
+        <v>-20.46</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.78692305</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-76.42552999999999</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>1755687540</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1756296000</v>
+      </c>
+      <c r="EH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="EK2" t="inlineStr">
         <is>
           <t>REGULAR</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>1775107808</v>
-      </c>
-      <c r="DM2" t="n">
+      <c r="EL2" t="b">
         <v>0</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>684725</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>5.54 - 27.35</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>-21.810001</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.79744065</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-78.69231000000001</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1755687540</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1756296000</v>
-      </c>
-      <c r="DY2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-4.98</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.3091998</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.0528619</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-9.352826</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.62800884</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>20</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>20</v>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1335488400000</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>5.54 - 5.54</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>YEONG GUAN ENERGY TECHNOLOGY GP</t>
-        </is>
       </c>
       <c r="EM2" t="inlineStr"/>
     </row>
